--- a/output/Leiloaria_Smart_Grupos_Facebook_COMPLETO.xlsx
+++ b/output/Leiloaria_Smart_Grupos_Facebook_COMPLETO.xlsx
@@ -622,17 +622,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1410240139266333</t>
+          <t>1709276312713836</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1410240139266333</t>
+          <t>https://www.facebook.com/groups/1709276312713836</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Imoveis usados e repasse em Salvador Bahia parcerias e trocas</t>
+          <t>Imóveis - Compra Venda Aluguel</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
@@ -657,17 +657,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1709276312713836</t>
+          <t>1410240139266333</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1709276312713836</t>
+          <t>https://www.facebook.com/groups/1410240139266333</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Imóveis - Compra Venda Aluguel</t>
+          <t>Imoveis usados e repasse em Salvador Bahia parcerias e trocas</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
@@ -692,17 +692,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>289651344710945</t>
+          <t>759761177003416</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/289651344710945</t>
+          <t>https://www.facebook.com/groups/759761177003416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de Casa em Salvador</t>
+          <t>GRUPO IMOBILIÁRIO compra e venda.</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
@@ -727,17 +727,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>759761177003416</t>
+          <t>289651344710945</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/759761177003416</t>
+          <t>https://www.facebook.com/groups/289651344710945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>GRUPO IMOBILIÁRIO compra e venda.</t>
+          <t>Aluguel de Casa em Salvador</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
@@ -762,17 +762,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>281364753085504</t>
+          <t>421680128199966</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/281364753085504</t>
+          <t>https://www.facebook.com/groups/421680128199966</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de Imóveis em Salvador é aqui</t>
+          <t>Aluguel de casas / apartamentos Salvador Bahia</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
@@ -797,17 +797,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1629856543977154</t>
+          <t>281364753085504</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1629856543977154</t>
+          <t>https://www.facebook.com/groups/281364753085504</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Aluguel Casas e Apartamentos Salvador</t>
+          <t>Aluguel de Imóveis em Salvador é aqui</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
@@ -832,17 +832,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>421680128199966</t>
+          <t>1629856543977154</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/421680128199966</t>
+          <t>https://www.facebook.com/groups/1629856543977154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de casas / apartamentos Salvador Bahia</t>
+          <t>Aluguel Casas e Apartamentos Salvador</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
@@ -972,17 +972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1410240139266333</t>
+          <t>1709276312713836</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1410240139266333</t>
+          <t>https://www.facebook.com/groups/1709276312713836</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Imoveis usados e repasse em Salvador Bahia parcerias e trocas</t>
+          <t>Imóveis - Compra Venda Aluguel</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1709276312713836</t>
+          <t>1410240139266333</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1709276312713836</t>
+          <t>https://www.facebook.com/groups/1410240139266333</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Imóveis - Compra Venda Aluguel</t>
+          <t>Imoveis usados e repasse em Salvador Bahia parcerias e trocas</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>289651344710945</t>
+          <t>759761177003416</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/289651344710945</t>
+          <t>https://www.facebook.com/groups/759761177003416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de Casa em Salvador</t>
+          <t>GRUPO IMOBILIÁRIO compra e venda.</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
@@ -1077,17 +1077,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>759761177003416</t>
+          <t>289651344710945</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/759761177003416</t>
+          <t>https://www.facebook.com/groups/289651344710945</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>GRUPO IMOBILIÁRIO compra e venda.</t>
+          <t>Aluguel de Casa em Salvador</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
@@ -1112,17 +1112,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>281364753085504</t>
+          <t>421680128199966</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/281364753085504</t>
+          <t>https://www.facebook.com/groups/421680128199966</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de Imóveis em Salvador é aqui</t>
+          <t>Aluguel de casas / apartamentos Salvador Bahia</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1629856543977154</t>
+          <t>281364753085504</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1629856543977154</t>
+          <t>https://www.facebook.com/groups/281364753085504</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Aluguel Casas e Apartamentos Salvador</t>
+          <t>Aluguel de Imóveis em Salvador é aqui</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>421680128199966</t>
+          <t>1629856543977154</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/421680128199966</t>
+          <t>https://www.facebook.com/groups/1629856543977154</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de casas / apartamentos Salvador Bahia</t>
+          <t>Aluguel Casas e Apartamentos Salvador</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1410240139266333</t>
+          <t>1709276312713836</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1410240139266333</t>
+          <t>https://www.facebook.com/groups/1709276312713836</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Imoveis usados e repasse em Salvador Bahia parcerias e trocas</t>
+          <t>Imóveis - Compra Venda Aluguel</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
@@ -1357,17 +1357,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1709276312713836</t>
+          <t>1410240139266333</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1709276312713836</t>
+          <t>https://www.facebook.com/groups/1410240139266333</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Imóveis - Compra Venda Aluguel</t>
+          <t>Imoveis usados e repasse em Salvador Bahia parcerias e trocas</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>289651344710945</t>
+          <t>759761177003416</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/289651344710945</t>
+          <t>https://www.facebook.com/groups/759761177003416</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de Casa em Salvador</t>
+          <t>GRUPO IMOBILIÁRIO compra e venda.</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>759761177003416</t>
+          <t>289651344710945</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/759761177003416</t>
+          <t>https://www.facebook.com/groups/289651344710945</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>GRUPO IMOBILIÁRIO compra e venda.</t>
+          <t>Aluguel de Casa em Salvador</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>281364753085504</t>
+          <t>421680128199966</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/281364753085504</t>
+          <t>https://www.facebook.com/groups/421680128199966</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de Imóveis em Salvador é aqui</t>
+          <t>Aluguel de casas / apartamentos Salvador Bahia</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
@@ -1497,17 +1497,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1629856543977154</t>
+          <t>281364753085504</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1629856543977154</t>
+          <t>https://www.facebook.com/groups/281364753085504</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Aluguel Casas e Apartamentos Salvador</t>
+          <t>Aluguel de Imóveis em Salvador é aqui</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
@@ -1532,17 +1532,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>421680128199966</t>
+          <t>1629856543977154</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/421680128199966</t>
+          <t>https://www.facebook.com/groups/1629856543977154</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de casas / apartamentos Salvador Bahia</t>
+          <t>Aluguel Casas e Apartamentos Salvador</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1410240139266333</t>
+          <t>1709276312713836</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1410240139266333</t>
+          <t>https://www.facebook.com/groups/1709276312713836</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Imoveis usados e repasse em Salvador Bahia parcerias e trocas</t>
+          <t>Imóveis - Compra Venda Aluguel</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1709276312713836</t>
+          <t>1410240139266333</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1709276312713836</t>
+          <t>https://www.facebook.com/groups/1410240139266333</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Imóveis - Compra Venda Aluguel</t>
+          <t>Imoveis usados e repasse em Salvador Bahia parcerias e trocas</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>289651344710945</t>
+          <t>759761177003416</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/289651344710945</t>
+          <t>https://www.facebook.com/groups/759761177003416</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de Casa em Salvador</t>
+          <t>GRUPO IMOBILIÁRIO compra e venda.</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>759761177003416</t>
+          <t>289651344710945</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/759761177003416</t>
+          <t>https://www.facebook.com/groups/289651344710945</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>GRUPO IMOBILIÁRIO compra e venda.</t>
+          <t>Aluguel de Casa em Salvador</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>281364753085504</t>
+          <t>421680128199966</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/281364753085504</t>
+          <t>https://www.facebook.com/groups/421680128199966</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de Imóveis em Salvador é aqui</t>
+          <t>Aluguel de casas / apartamentos Salvador Bahia</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
@@ -1847,17 +1847,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1629856543977154</t>
+          <t>281364753085504</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1629856543977154</t>
+          <t>https://www.facebook.com/groups/281364753085504</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Aluguel Casas e Apartamentos Salvador</t>
+          <t>Aluguel de Imóveis em Salvador é aqui</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>421680128199966</t>
+          <t>1629856543977154</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/421680128199966</t>
+          <t>https://www.facebook.com/groups/1629856543977154</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de casas / apartamentos Salvador Bahia</t>
+          <t>Aluguel Casas e Apartamentos Salvador</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>486490283107814</t>
+          <t>599734292074642</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/486490283107814</t>
+          <t>https://www.facebook.com/groups/599734292074642</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>IMÓVEIS UBERLÂNDIA - Aluguel e Venda de imóveis.</t>
+          <t>CASAS PRA ALUGAR DIRETO COM O DONO UBERLANDIA</t>
         </is>
       </c>
       <c r="G45" s="4" t="n">
@@ -2057,17 +2057,17 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1420946561546386</t>
+          <t>486490283107814</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1420946561546386</t>
+          <t>https://www.facebook.com/groups/486490283107814</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Imoveis Uberlandia ( VENDAS)</t>
+          <t>IMÓVEIS UBERLÂNDIA - Aluguel e Venda de imóveis.</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
@@ -2092,17 +2092,17 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>599734292074642</t>
+          <t>1420946561546386</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/599734292074642</t>
+          <t>https://www.facebook.com/groups/1420946561546386</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>CASAS PRA ALUGAR DIRETO COM O DONO UBERLANDIA</t>
+          <t>Imoveis Uberlandia ( VENDAS)</t>
         </is>
       </c>
       <c r="G47" s="4" t="n">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>578049284042411</t>
+          <t>3472477749739828</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/578049284042411</t>
+          <t>https://www.facebook.com/groups/3472477749739828</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>OLX Brasília &amp; Entorno DF-GO</t>
+          <t>Divulgação Brasília - DF</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
@@ -2302,17 +2302,17 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>512174575476547</t>
+          <t>578049284042411</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/512174575476547</t>
+          <t>https://www.facebook.com/groups/578049284042411</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>IMOVEIS DF</t>
+          <t>OLX Brasília &amp; Entorno DF-GO</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
@@ -2337,17 +2337,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>3472477749739828</t>
+          <t>512174575476547</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/3472477749739828</t>
+          <t>https://www.facebook.com/groups/512174575476547</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Divulgação Brasília - DF</t>
+          <t>IMOVEIS DF</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>177287232312262</t>
+          <t>672328276132511</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/177287232312262</t>
+          <t>https://www.facebook.com/groups/672328276132511</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Compra, Venda e Aluguel de imóveis DF</t>
+          <t>Brasília DF mercado livre</t>
         </is>
       </c>
       <c r="G57" s="4" t="n">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>672328276132511</t>
+          <t>138334086805338</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/672328276132511</t>
+          <t>https://www.facebook.com/groups/138334086805338</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Brasília DF mercado livre</t>
+          <t>Aluguel de imóveis no DF - Direto com proprietário - Sem fiador!</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
@@ -2512,17 +2512,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>1430547060568724</t>
+          <t>1008161639232670</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1430547060568724</t>
+          <t>https://www.facebook.com/groups/1008161639232670</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de casas em Brasília</t>
+          <t>VENDAS E TROCAS Brasília-DF!!</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
@@ -2547,17 +2547,17 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>110954989246687</t>
+          <t>177287232312262</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/110954989246687</t>
+          <t>https://www.facebook.com/groups/177287232312262</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Venda de imóveis no Guará DF</t>
+          <t>Compra, Venda e Aluguel de imóveis DF</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
@@ -2582,17 +2582,17 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>138334086805338</t>
+          <t>1430547060568724</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/138334086805338</t>
+          <t>https://www.facebook.com/groups/1430547060568724</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de imóveis no DF - Direto com proprietário - Sem fiador!</t>
+          <t>Aluguel de casas em Brasília</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
@@ -2602,17 +2602,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Caonze Rio de Janeiro</t>
+          <t>Rio de Janeiro RJ</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>bairro</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2631,23 +2631,23 @@
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>60000</v>
+        <v>6748000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Caonze Rio de Janeiro</t>
+          <t>Rio de Janeiro RJ</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>bairro</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2666,23 +2666,23 @@
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>60000</v>
+        <v>6748000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Caonze Rio de Janeiro</t>
+          <t>Rio de Janeiro RJ</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>bairro</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2701,93 +2701,93 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>60000</v>
+        <v>6748000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Caonze Rio de Janeiro</t>
+          <t>Rio de Janeiro RJ</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>bairro</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>746608938793612</t>
+          <t>1008386497889162</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/746608938793612</t>
+          <t>https://www.facebook.com/groups/1008386497889162</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>ALUGUEL APARTAMENTO - RIO DE JANEIRO</t>
+          <t>VENDA, TROCA, ALUGA-SE CASAS NO RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>60000</v>
+        <v>6748000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Caonze Rio de Janeiro</t>
+          <t>Rio de Janeiro RJ</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>bairro</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1008386497889162</t>
+          <t>746608938793612</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1008386497889162</t>
+          <t>https://www.facebook.com/groups/746608938793612</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>VENDA, TROCA, ALUGA-SE CASAS NO RIO DE JANEIRO</t>
+          <t>ALUGUEL APARTAMENTO - RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>60000</v>
+        <v>6748000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Caonze Rio de Janeiro</t>
+          <t>Rio de Janeiro RJ</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>bairro</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2806,93 +2806,93 @@
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>60000</v>
+        <v>6748000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Caonze Rio de Janeiro</t>
+          <t>Rio de Janeiro RJ</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>bairro</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>323866948749057</t>
+          <t>967832216603467</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/323866948749057</t>
+          <t>https://www.facebook.com/groups/967832216603467</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Vendas de casas em qualquer localidade do Rio De Janeiro</t>
+          <t>Aluguel e Venda de Imóveis - Niterói - RJ</t>
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>60000</v>
+        <v>6748000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Caonze Rio de Janeiro</t>
+          <t>Rio de Janeiro RJ</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>bairro</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>967832216603467</t>
+          <t>323866948749057</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/967832216603467</t>
+          <t>https://www.facebook.com/groups/323866948749057</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Aluguel e Venda de Imóveis - Niterói - RJ</t>
+          <t>Vendas de casas em qualquer localidade do Rio De Janeiro</t>
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>60000</v>
+        <v>6748000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Caonze Rio de Janeiro</t>
+          <t>Rio de Janeiro RJ</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>bairro</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2911,23 +2911,23 @@
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>60000</v>
+        <v>6748000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Caonze Rio de Janeiro</t>
+          <t>Rio de Janeiro RJ</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>bairro</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>60000</v>
+        <v>6748000</v>
       </c>
     </row>
     <row r="72">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3072,17 +3072,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>1711182952539528</t>
+          <t>2421592694770375</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1711182952539528</t>
+          <t>https://www.facebook.com/groups/2421592694770375</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Aluga-se ou vende-se em São Paulo Capital</t>
+          <t>SÓ IMÓVEIS</t>
         </is>
       </c>
       <c r="G75" s="4" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3107,17 +3107,17 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>2421592694770375</t>
+          <t>1711182952539528</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2421592694770375</t>
+          <t>https://www.facebook.com/groups/1711182952539528</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>SÓ IMÓVEIS</t>
+          <t>Aluga-se ou vende-se em São Paulo Capital</t>
         </is>
       </c>
       <c r="G76" s="4" t="n">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>987794728082712</t>
+          <t>1600618146887233</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/987794728082712</t>
+          <t>https://www.facebook.com/groups/1600618146887233</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>GRUPO PARA VENDAS DE IMÓVEIS-TODAS AS REGIÕES DE SÃO PAULO!!!</t>
+          <t>Anuncio de Imóveis São Paulo e Região - MercadoClassificado</t>
         </is>
       </c>
       <c r="G79" s="4" t="n">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>1600618146887233</t>
+          <t>937722058204370</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1600618146887233</t>
+          <t>https://www.facebook.com/groups/937722058204370</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Anuncio de Imóveis São Paulo e Região - MercadoClassificado</t>
+          <t>VENDA DE IMÓVEIS SÃO PAULO SP</t>
         </is>
       </c>
       <c r="G81" s="4" t="n">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>446140159762455</t>
+          <t>2102242643119961</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/446140159762455</t>
+          <t>https://www.facebook.com/groups/2102242643119961</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Joga pra rolo Jacarepaguá</t>
+          <t>joga pra rolo jacarepaguá</t>
         </is>
       </c>
       <c r="G85" s="4" t="n">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>292788034837008</t>
+          <t>446140159762455</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/292788034837008</t>
+          <t>https://www.facebook.com/groups/446140159762455</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Jacarepaguá - RJ - Aluguel</t>
+          <t>Joga pra rolo Jacarepaguá</t>
         </is>
       </c>
       <c r="G86" s="4" t="n">
@@ -3492,17 +3492,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>724518743105134</t>
+          <t>292788034837008</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/724518743105134</t>
+          <t>https://www.facebook.com/groups/292788034837008</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Joga pra Rolo Jacarepaguá</t>
+          <t>Jacarepaguá - RJ - Aluguel</t>
         </is>
       </c>
       <c r="G87" s="4" t="n">
@@ -3527,17 +3527,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1808839059441804</t>
+          <t>367017873424533</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1808839059441804</t>
+          <t>https://www.facebook.com/groups/367017873424533</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Compra, venda e aluguel de casas em Jacarepaguá</t>
+          <t>ALUGUEL RESIDENCIAL - JACAREPAGUÁ</t>
         </is>
       </c>
       <c r="G88" s="4" t="n">
@@ -3562,17 +3562,17 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>367017873424533</t>
+          <t>1808839059441804</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/367017873424533</t>
+          <t>https://www.facebook.com/groups/1808839059441804</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>ALUGUEL RESIDENCIAL - JACAREPAGUÁ</t>
+          <t>Compra, venda e aluguel de casas em Jacarepaguá</t>
         </is>
       </c>
       <c r="G89" s="4" t="n">
@@ -3597,17 +3597,17 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1751427231747732</t>
+          <t>724518743105134</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1751427231747732</t>
+          <t>https://www.facebook.com/groups/724518743105134</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Bom Negócio - Jacarepaguá</t>
+          <t>Joga pra Rolo Jacarepaguá</t>
         </is>
       </c>
       <c r="G90" s="4" t="n">
@@ -3632,17 +3632,17 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>2060628417302137</t>
+          <t>1751427231747732</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2060628417302137</t>
+          <t>https://www.facebook.com/groups/1751427231747732</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>JOGA PRA ROLO ⭐ JACAREPAGUÁ</t>
+          <t>Bom Negócio - Jacarepaguá</t>
         </is>
       </c>
       <c r="G91" s="4" t="n">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1629014270588031</t>
+          <t>260777085618037</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1629014270588031</t>
+          <t>https://www.facebook.com/groups/260777085618037</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>NATAL - RN</t>
+          <t>NATAL-RN</t>
         </is>
       </c>
       <c r="G96" s="4" t="n">
@@ -3842,17 +3842,17 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>260777085618037</t>
+          <t>1629014270588031</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/260777085618037</t>
+          <t>https://www.facebook.com/groups/1629014270588031</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>NATAL-RN</t>
+          <t>NATAL - RN</t>
         </is>
       </c>
       <c r="G97" s="4" t="n">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1671734279783612</t>
+          <t>838535949501191</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1671734279783612</t>
+          <t>https://www.facebook.com/groups/838535949501191</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Desapega Casas&amp;Terrenos - Natal-RN e adjacências</t>
+          <t>Classificados Imobiliários do RN</t>
         </is>
       </c>
       <c r="G100" s="4" t="n">
@@ -3982,17 +3982,17 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>408074519366656</t>
+          <t>1671734279783612</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/408074519366656</t>
+          <t>https://www.facebook.com/groups/1671734279783612</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Classificado Natal - Rn ( compra e venda )</t>
+          <t>Desapega Casas&amp;Terrenos - Natal-RN e adjacências</t>
         </is>
       </c>
       <c r="G101" s="4" t="n">
@@ -4122,17 +4122,17 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>416642188460989</t>
+          <t>1413652495579159</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/416642188460989</t>
+          <t>https://www.facebook.com/groups/1413652495579159</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>ALUGAR APARTAMENTO EM CURITIBA</t>
+          <t>Araucária - Curitiba e Região Metropolitana - PR41</t>
         </is>
       </c>
       <c r="G105" s="4" t="n">
@@ -4157,17 +4157,17 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>1413652495579159</t>
+          <t>416642188460989</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1413652495579159</t>
+          <t>https://www.facebook.com/groups/416642188460989</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Araucária - Curitiba e Região Metropolitana - PR41</t>
+          <t>ALUGAR APARTAMENTO EM CURITIBA</t>
         </is>
       </c>
       <c r="G106" s="4" t="n">
@@ -4192,17 +4192,17 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>142387275936424</t>
+          <t>314043949721427</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/142387275936424</t>
+          <t>https://www.facebook.com/groups/314043949721427</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Imóveis Locação e Venda Curitiba e Região</t>
+          <t>VENDA e PERMUTA Imóveis Curitiba.</t>
         </is>
       </c>
       <c r="G107" s="4" t="n">
@@ -4227,17 +4227,17 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>314043949721427</t>
+          <t>142387275936424</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/314043949721427</t>
+          <t>https://www.facebook.com/groups/142387275936424</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>VENDA e PERMUTA Imóveis Curitiba.</t>
+          <t>Imóveis Locação e Venda Curitiba e Região</t>
         </is>
       </c>
       <c r="G108" s="4" t="n">
@@ -4332,17 +4332,17 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>348481436061103</t>
+          <t>406861759415118</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/348481436061103</t>
+          <t>https://www.facebook.com/groups/406861759415118</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Aluguel Direto Curitiba | Imóveis e Quartos</t>
+          <t>IMÓVEIS CURITIBA E REGIÃO</t>
         </is>
       </c>
       <c r="G111" s="4" t="n">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Pessoa</t>
+          <t>João Pessoa</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Pessoa</t>
+          <t>João Pessoa</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Pessoa</t>
+          <t>João Pessoa</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Pessoa</t>
+          <t>João Pessoa</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Pessoa</t>
+          <t>João Pessoa</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -4507,17 +4507,17 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>189263592330100</t>
+          <t>988870378244733</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/189263592330100</t>
+          <t>https://www.facebook.com/groups/988870378244733</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>GRUPO EXCLUSIVO DE IMÓVEIS EM JOÃO PESSOA/PB</t>
+          <t>Apartamentos e Casas em João Pessoa - PB . Imóveis para vender e alugar .</t>
         </is>
       </c>
       <c r="G116" s="4" t="n">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Pessoa</t>
+          <t>João Pessoa</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -4542,17 +4542,17 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>988870378244733</t>
+          <t>189263592330100</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/988870378244733</t>
+          <t>https://www.facebook.com/groups/189263592330100</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Apartamentos e Casas em João Pessoa - PB . Imóveis para vender e alugar .</t>
+          <t>GRUPO EXCLUSIVO DE IMÓVEIS EM JOÃO PESSOA/PB</t>
         </is>
       </c>
       <c r="G117" s="4" t="n">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Pessoa</t>
+          <t>João Pessoa</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>806832416413410</t>
+          <t>1390556161163555</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/806832416413410</t>
+          <t>https://www.facebook.com/groups/1390556161163555</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Pessoa</t>
+          <t>João Pessoa</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -4612,17 +4612,17 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>1390556161163555</t>
+          <t>462076824993059</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1390556161163555</t>
+          <t>https://www.facebook.com/groups/462076824993059</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Negócios Imobiliários</t>
+          <t>Aluguel de Kitnets / João Pessoa-PB</t>
         </is>
       </c>
       <c r="G119" s="4" t="n">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Pessoa</t>
+          <t>João Pessoa</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -4647,17 +4647,17 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>462076824993059</t>
+          <t>2421592694770375</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/462076824993059</t>
+          <t>https://www.facebook.com/groups/2421592694770375</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de Kitnets / João Pessoa-PB</t>
+          <t>SÓ IMÓVEIS</t>
         </is>
       </c>
       <c r="G120" s="4" t="n">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Pessoa</t>
+          <t>João Pessoa</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -4717,17 +4717,17 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>746381090469402</t>
+          <t>478958175585106</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/746381090469402</t>
+          <t>https://www.facebook.com/groups/478958175585106</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Aluga rápido Campinas SP</t>
+          <t>ALUGA IMOVEIS CAMPINAS</t>
         </is>
       </c>
       <c r="G122" s="4" t="n">
@@ -4752,17 +4752,17 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>478958175585106</t>
+          <t>746381090469402</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/478958175585106</t>
+          <t>https://www.facebook.com/groups/746381090469402</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>ALUGA IMOVEIS CAMPINAS</t>
+          <t>Aluga rápido Campinas SP</t>
         </is>
       </c>
       <c r="G123" s="4" t="n">
@@ -4787,17 +4787,17 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>585342064859489</t>
+          <t>769432750365913</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/585342064859489</t>
+          <t>https://www.facebook.com/groups/769432750365913</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>IMOVEIS CAMPINAS</t>
+          <t>ALUGUEL DE CASAS CAMPINAS E REGIAO</t>
         </is>
       </c>
       <c r="G124" s="4" t="n">
@@ -4822,17 +4822,17 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>718230786283345</t>
+          <t>585342064859489</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/718230786283345</t>
+          <t>https://www.facebook.com/groups/585342064859489</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>PROCURA-SE, Aluguel em Campinas / SP - SOMENTE com o Proprietário</t>
+          <t>IMOVEIS CAMPINAS</t>
         </is>
       </c>
       <c r="G125" s="4" t="n">
@@ -4857,17 +4857,17 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>679290124780920</t>
+          <t>718230786283345</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/679290124780920</t>
+          <t>https://www.facebook.com/groups/718230786283345</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Venda Imóveis em Campinas e Região</t>
+          <t>PROCURA-SE, Aluguel em Campinas / SP - SOMENTE com o Proprietário</t>
         </is>
       </c>
       <c r="G126" s="4" t="n">
@@ -4892,17 +4892,17 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>392724724232422</t>
+          <t>679290124780920</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/392724724232422</t>
+          <t>https://www.facebook.com/groups/679290124780920</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>IMÓVEIS À VENDA EM CAMPINAS E REGIÃO</t>
+          <t>Venda Imóveis em Campinas e Região</t>
         </is>
       </c>
       <c r="G127" s="4" t="n">
@@ -4927,17 +4927,17 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>2449299932046657</t>
+          <t>1090978760977502</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2449299932046657</t>
+          <t>https://www.facebook.com/groups/1090978760977502</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Olx Campinas SP</t>
+          <t>Repúblicas em Campinas SP – Moradia, Kitnets, Mobília &amp; Compra e Venda</t>
         </is>
       </c>
       <c r="G128" s="4" t="n">
@@ -4962,17 +4962,17 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>340499789698867</t>
+          <t>392724724232422</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/340499789698867</t>
+          <t>https://www.facebook.com/groups/392724724232422</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Vendas e Aluga-se Imoveis Campinas e Região</t>
+          <t>IMÓVEIS À VENDA EM CAMPINAS E REGIÃO</t>
         </is>
       </c>
       <c r="G129" s="4" t="n">
@@ -4997,17 +4997,17 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>1181749210276570</t>
+          <t>2449299932046657</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1181749210276570</t>
+          <t>https://www.facebook.com/groups/2449299932046657</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>vendas e aluguel de casas Campinas SP</t>
+          <t>Olx Campinas SP</t>
         </is>
       </c>
       <c r="G130" s="4" t="n">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>231124760565635</t>
+          <t>629462533831621</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/231124760565635</t>
+          <t>https://www.facebook.com/groups/629462533831621</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>locação de imóveis - particular e imobiliária</t>
+          <t>Portal de Imóveis no ABCD e SP</t>
         </is>
       </c>
       <c r="G139" s="4" t="n">
@@ -5347,17 +5347,17 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>190958316768295</t>
+          <t>231124760565635</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/190958316768295</t>
+          <t>https://www.facebook.com/groups/231124760565635</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Imóveis no Butantã Vendas e locações</t>
+          <t>locação de imóveis - particular e imobiliária</t>
         </is>
       </c>
       <c r="G140" s="4" t="n">
@@ -5487,17 +5487,17 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>8716938165081656</t>
+          <t>383200198689909</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/8716938165081656</t>
+          <t>https://www.facebook.com/groups/383200198689909</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>LOCAÇÃO E VENDA CAMAÇARI E ADJACÊNCIAS.</t>
+          <t>Aluga e vende casas e apartamentos de camaçari</t>
         </is>
       </c>
       <c r="G144" s="4" t="n">
@@ -5522,17 +5522,17 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>383200198689909</t>
+          <t>8716938165081656</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/383200198689909</t>
+          <t>https://www.facebook.com/groups/8716938165081656</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Aluga e vende casas e apartamentos de camaçari</t>
+          <t>LOCAÇÃO E VENDA CAMAÇARI E ADJACÊNCIAS.</t>
         </is>
       </c>
       <c r="G145" s="4" t="n">
@@ -5942,17 +5942,17 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>322675271602484</t>
+          <t>940542261893023</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/322675271602484</t>
+          <t>https://www.facebook.com/groups/940542261893023</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Venda e aluguel de casas Barra bonita e Região.</t>
+          <t>Casas prá alugar você 🫵 encontra aqui Barretos SP</t>
         </is>
       </c>
       <c r="G157" s="4" t="n">
@@ -5977,17 +5977,17 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>940542261893023</t>
+          <t>322675271602484</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/940542261893023</t>
+          <t>https://www.facebook.com/groups/322675271602484</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Casas prá alugar você 🫵 encontra aqui Barretos SP</t>
+          <t>Venda e aluguel de casas Barra bonita e Região.</t>
         </is>
       </c>
       <c r="G158" s="4" t="n">
@@ -6047,17 +6047,17 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>290149347749541</t>
+          <t>1752140968407863</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/290149347749541</t>
+          <t>https://www.facebook.com/groups/1752140968407863</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>CLASSIFICADOS DE PEREIRA BARRETO</t>
+          <t>Aluguel e Venda de Casas Barreiras-Bahia</t>
         </is>
       </c>
       <c r="G160" s="4" t="n">
@@ -6082,17 +6082,17 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>1752140968407863</t>
+          <t>290149347749541</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1752140968407863</t>
+          <t>https://www.facebook.com/groups/290149347749541</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Aluguel e Venda de Casas Barreiras-Bahia</t>
+          <t>CLASSIFICADOS DE PEREIRA BARRETO</t>
         </is>
       </c>
       <c r="G161" s="4" t="n">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -6257,17 +6257,17 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>265102866928704</t>
+          <t>2664354250396276</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/265102866928704</t>
+          <t>https://www.facebook.com/groups/2664354250396276</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Imóveis em São José dos Campos</t>
+          <t>Casa Kitnet Apto para alugar em São José Palhoça Biguaçu e Florianópolis</t>
         </is>
       </c>
       <c r="G166" s="4" t="n">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -6292,17 +6292,17 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>2664354250396276</t>
+          <t>265102866928704</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2664354250396276</t>
+          <t>https://www.facebook.com/groups/265102866928704</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Casa Kitnet Apto para alugar em São José Palhoça Biguaçu e Florianópolis</t>
+          <t>Imóveis em São José dos Campos</t>
         </is>
       </c>
       <c r="G167" s="4" t="n">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -6362,17 +6362,17 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>946345205433512</t>
+          <t>1653060044800480</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/946345205433512</t>
+          <t>https://www.facebook.com/groups/1653060044800480</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>ALUGUEL E VENDA DE IMÓVEIS SÃO JOSÉ DOS CAMPOS</t>
+          <t>Negócios Imobiliários região São José do Rio Preto</t>
         </is>
       </c>
       <c r="G169" s="4" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -6397,17 +6397,17 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>401727979888673</t>
+          <t>119102495399270</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/401727979888673</t>
+          <t>https://www.facebook.com/groups/119102495399270</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>OFERTAS DE IMÓVEIS EM SÃO JOSÉ DOS CAMPOS</t>
+          <t>Imoveis para Alugar em São José dos Campos</t>
         </is>
       </c>
       <c r="G170" s="4" t="n">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -6432,17 +6432,17 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>119102495399270</t>
+          <t>401727979888673</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/119102495399270</t>
+          <t>https://www.facebook.com/groups/401727979888673</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>Imoveis para Alugar em São José dos Campos</t>
+          <t>OFERTAS DE IMÓVEIS EM SÃO JOSÉ DOS CAMPOS</t>
         </is>
       </c>
       <c r="G171" s="4" t="n">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G172" s="4" t="n">
-        <v>364254</v>
+        <v>11451245</v>
       </c>
     </row>
     <row r="173">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="G173" s="4" t="n">
-        <v>364254</v>
+        <v>11451245</v>
       </c>
     </row>
     <row r="174">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="G174" s="4" t="n">
-        <v>364254</v>
+        <v>11451245</v>
       </c>
     </row>
     <row r="175">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -6572,21 +6572,21 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>413671432167041</t>
+          <t>218145011856001</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/413671432167041</t>
+          <t>https://www.facebook.com/groups/218145011856001</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Classificados de Imóveis em Ribeirão Preto SP</t>
+          <t>Imoveis Rio Preto e Região</t>
         </is>
       </c>
       <c r="G175" s="4" t="n">
-        <v>364254</v>
+        <v>11451245</v>
       </c>
     </row>
     <row r="176">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -6607,21 +6607,21 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>218145011856001</t>
+          <t>716548046447078</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/218145011856001</t>
+          <t>https://www.facebook.com/groups/716548046447078</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Imoveis Rio Preto e Região</t>
+          <t>Aluga-se Imóveis em Rio Preto</t>
         </is>
       </c>
       <c r="G176" s="4" t="n">
-        <v>364254</v>
+        <v>11451245</v>
       </c>
     </row>
     <row r="177">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -6642,21 +6642,21 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>716548046447078</t>
+          <t>661671595037136</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/716548046447078</t>
+          <t>https://www.facebook.com/groups/661671595037136</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Aluga-se Imóveis em Rio Preto</t>
+          <t>casas pra alugar São José Do Rio Preto</t>
         </is>
       </c>
       <c r="G177" s="4" t="n">
-        <v>364254</v>
+        <v>11451245</v>
       </c>
     </row>
     <row r="178">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -6677,21 +6677,21 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>661671595037136</t>
+          <t>642891259063811</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/661671595037136</t>
+          <t>https://www.facebook.com/groups/642891259063811</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>casas pra alugar São José Do Rio Preto</t>
+          <t>SÓ IMÓVEIS RIO PRETO</t>
         </is>
       </c>
       <c r="G178" s="4" t="n">
-        <v>364254</v>
+        <v>11451245</v>
       </c>
     </row>
     <row r="179">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -6712,21 +6712,21 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>962747927100689</t>
+          <t>2995806247271339</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/962747927100689</t>
+          <t>https://www.facebook.com/groups/2995806247271339</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>CLASSIFICADOS MEU IMÓVEL - RIO PRETO E REGIÃO</t>
+          <t>Casa Direto com proprietário Ribeirão Preto Sp</t>
         </is>
       </c>
       <c r="G179" s="4" t="n">
-        <v>364254</v>
+        <v>11451245</v>
       </c>
     </row>
     <row r="180">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -6747,21 +6747,21 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>642891259063811</t>
+          <t>850238701726467</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/642891259063811</t>
+          <t>https://www.facebook.com/groups/850238701726467</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>SÓ IMÓVEIS RIO PRETO</t>
+          <t>Imóveis São José do Rio Preto</t>
         </is>
       </c>
       <c r="G180" s="4" t="n">
-        <v>364254</v>
+        <v>11451245</v>
       </c>
     </row>
     <row r="181">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -6782,21 +6782,21 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>850238701726467</t>
+          <t>2421592694770375</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/850238701726467</t>
+          <t>https://www.facebook.com/groups/2421592694770375</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Imóveis São José do Rio Preto</t>
+          <t>SÓ IMÓVEIS</t>
         </is>
       </c>
       <c r="G181" s="4" t="n">
-        <v>364254</v>
+        <v>11451245</v>
       </c>
     </row>
     <row r="182">
@@ -6922,17 +6922,17 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>585500093036805</t>
+          <t>1628879560986072</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/585500093036805</t>
+          <t>https://www.facebook.com/groups/1628879560986072</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Casas para alugar - LORENA SP</t>
+          <t>Locação e venda de imóveis</t>
         </is>
       </c>
       <c r="G185" s="4" t="n">
@@ -6957,17 +6957,17 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>1628879560986072</t>
+          <t>2421592694770375</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1628879560986072</t>
+          <t>https://www.facebook.com/groups/2421592694770375</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Locação e venda de imóveis</t>
+          <t>SÓ IMÓVEIS</t>
         </is>
       </c>
       <c r="G186" s="4" t="n">
@@ -6992,17 +6992,17 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2421592694770375</t>
+          <t>585500093036805</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2421592694770375</t>
+          <t>https://www.facebook.com/groups/585500093036805</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>SÓ IMÓVEIS</t>
+          <t>Casas para alugar - LORENA SP</t>
         </is>
       </c>
       <c r="G187" s="4" t="n">
@@ -7027,17 +7027,17 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>1031386250667479</t>
+          <t>1013597310697543</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1031386250667479</t>
+          <t>https://www.facebook.com/groups/1013597310697543</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>VENDA IMÓVEL LINS</t>
+          <t>TROCA E VENDAS LORENA SP</t>
         </is>
       </c>
       <c r="G188" s="4" t="n">
@@ -7062,17 +7062,17 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>1013597310697543</t>
+          <t>1031386250667479</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1013597310697543</t>
+          <t>https://www.facebook.com/groups/1031386250667479</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>TROCA E VENDAS LORENA SP</t>
+          <t>VENDA IMÓVEL LINS</t>
         </is>
       </c>
       <c r="G189" s="4" t="n">
@@ -7272,17 +7272,17 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>299788133520600</t>
+          <t>859721384169497</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/299788133520600</t>
+          <t>https://www.facebook.com/groups/859721384169497</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Whatsapp Bebedouro - SP</t>
+          <t>Bebedouro desapega</t>
         </is>
       </c>
       <c r="G195" s="4" t="n">
@@ -7342,17 +7342,17 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>859721384169497</t>
+          <t>299788133520600</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/859721384169497</t>
+          <t>https://www.facebook.com/groups/299788133520600</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Bebedouro desapega</t>
+          <t>Whatsapp Bebedouro - SP</t>
         </is>
       </c>
       <c r="G197" s="4" t="n">
@@ -7377,17 +7377,17 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>366804718102998</t>
+          <t>787232834686501</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/366804718102998</t>
+          <t>https://www.facebook.com/groups/787232834686501</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>ALUGUEL CASAS E KITNET BEBEDOURO</t>
+          <t>BRECHÓ -BEBEDOURO -SP</t>
         </is>
       </c>
       <c r="G198" s="4" t="n">
@@ -7412,17 +7412,17 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>1093452076128780</t>
+          <t>366804718102998</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1093452076128780</t>
+          <t>https://www.facebook.com/groups/366804718102998</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Negócio Rápido Bebedouro SP</t>
+          <t>ALUGUEL CASAS E KITNET BEBEDOURO</t>
         </is>
       </c>
       <c r="G199" s="4" t="n">
@@ -7447,17 +7447,17 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>787232834686501</t>
+          <t>543716965686617</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/787232834686501</t>
+          <t>https://www.facebook.com/groups/543716965686617</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>BRECHÓ -BEBEDOURO -SP</t>
+          <t>COMPREI NO FACE BEBEDOURO-SP</t>
         </is>
       </c>
       <c r="G200" s="4" t="n">
@@ -7482,17 +7482,17 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>1590043247908205</t>
+          <t>1093452076128780</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1590043247908205</t>
+          <t>https://www.facebook.com/groups/1093452076128780</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>BOM NEGÓCIO BEBEDOURO-SP</t>
+          <t>Negócio Rápido Bebedouro SP</t>
         </is>
       </c>
       <c r="G201" s="4" t="n">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Leopoldo</t>
+          <t>São Leopoldo</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Leopoldo</t>
+          <t>São Leopoldo</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Leopoldo</t>
+          <t>São Leopoldo</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -7587,17 +7587,17 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>1236836023002743</t>
+          <t>247310349097813</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1236836023002743</t>
+          <t>https://www.facebook.com/groups/247310349097813</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Vendas de Casa e Terrenos em São Leopoldo/RS - BRICK's e vendas diversas</t>
+          <t>Vendas Ou Aluguéis Diretos São Leopoldo</t>
         </is>
       </c>
       <c r="G204" s="4" t="n">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Leopoldo</t>
+          <t>São Leopoldo</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -7622,17 +7622,17 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>247310349097813</t>
+          <t>1236836023002743</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/247310349097813</t>
+          <t>https://www.facebook.com/groups/1236836023002743</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Vendas Ou Aluguéis Diretos São Leopoldo</t>
+          <t>Vendas de Casa e Terrenos em São Leopoldo/RS - BRICK's e vendas diversas</t>
         </is>
       </c>
       <c r="G205" s="4" t="n">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Leopoldo</t>
+          <t>São Leopoldo</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Leopoldo</t>
+          <t>São Leopoldo</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Leopoldo</t>
+          <t>São Leopoldo</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Leopoldo</t>
+          <t>São Leopoldo</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Leopoldo</t>
+          <t>São Leopoldo</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -7797,17 +7797,17 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>1356339187834182</t>
+          <t>1628879560986072</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1356339187834182</t>
+          <t>https://www.facebook.com/groups/1628879560986072</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>Classificados Compra, Venda e Locação de Imóveis em São Leopoldo - RS</t>
+          <t>Locação e venda de imóveis</t>
         </is>
       </c>
       <c r="G210" s="4" t="n">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Leopoldo</t>
+          <t>São Leopoldo</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -7832,17 +7832,17 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>1628879560986072</t>
+          <t>1356339187834182</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1628879560986072</t>
+          <t>https://www.facebook.com/groups/1356339187834182</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>Locação e venda de imóveis</t>
+          <t>Classificados Compra, Venda e Locação de Imóveis em São Leopoldo - RS</t>
         </is>
       </c>
       <c r="G211" s="4" t="n">
@@ -8202,12 +8202,12 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Seguro BA</t>
+          <t>Porto Seguro BA</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -8217,17 +8217,17 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>2901676496639800</t>
+          <t>1530931133920786</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2901676496639800</t>
+          <t>https://www.facebook.com/groups/1530931133920786</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>Financiamento de Imóveis Direto com Proprietário</t>
+          <t>Porto Seguro Imóveis - aluguel mensal e temporada</t>
         </is>
       </c>
       <c r="G222" s="4" t="n">
@@ -8237,12 +8237,12 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Seguro BA</t>
+          <t>Porto Seguro BA</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>1709276312713836</t>
+          <t>1025284027598361</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1709276312713836</t>
+          <t>https://www.facebook.com/groups/1025284027598361</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>Imóveis - Compra Venda Aluguel</t>
+          <t>OLX PORTO SEGURO</t>
         </is>
       </c>
       <c r="G223" s="4" t="n">
@@ -8272,12 +8272,12 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Seguro BA</t>
+          <t>Porto Seguro BA</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -8287,17 +8287,17 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>231124760565635</t>
+          <t>2155118574796571</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/231124760565635</t>
+          <t>https://www.facebook.com/groups/2155118574796571</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>locação de imóveis - particular e imobiliária</t>
+          <t>Divulgações De Imóveis Porto Seguro</t>
         </is>
       </c>
       <c r="G224" s="4" t="n">
@@ -8307,12 +8307,12 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Seguro BA</t>
+          <t>Porto Seguro BA</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -8322,17 +8322,17 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>1921659474552846</t>
+          <t>109312423104243</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1921659474552846</t>
+          <t>https://www.facebook.com/groups/109312423104243</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>Imobiliária Virtual-Grupo de Negócios Imobiliários-Compras-Vendas-Trocas</t>
+          <t>vendas porto seguro</t>
         </is>
       </c>
       <c r="G225" s="4" t="n">
@@ -8342,12 +8342,12 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Seguro BA</t>
+          <t>Porto Seguro BA</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -8357,17 +8357,17 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>1390556161163555</t>
+          <t>1759433114365365</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1390556161163555</t>
+          <t>https://www.facebook.com/groups/1759433114365365</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>Negócios Imobiliários</t>
+          <t>Aluguel MENSAL Porto Seguro</t>
         </is>
       </c>
       <c r="G226" s="4" t="n">
@@ -8377,12 +8377,12 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Seguro BA</t>
+          <t>Porto Seguro BA</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -8392,17 +8392,17 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>806832416413410</t>
+          <t>1602916833253587</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/806832416413410</t>
+          <t>https://www.facebook.com/groups/1602916833253587</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>Negócios Imobiliários</t>
+          <t>Venda e Troca de Porto Seguro</t>
         </is>
       </c>
       <c r="G227" s="4" t="n">
@@ -8412,12 +8412,12 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Seguro BA</t>
+          <t>Porto Seguro BA</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -8427,17 +8427,17 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>759761177003416</t>
+          <t>341768449689562</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/759761177003416</t>
+          <t>https://www.facebook.com/groups/341768449689562</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>GRUPO IMOBILIÁRIO compra e venda.</t>
+          <t>PORTO SEGURO ALUGUÉIS</t>
         </is>
       </c>
       <c r="G228" s="4" t="n">
@@ -8447,12 +8447,12 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Seguro BA</t>
+          <t>Porto Seguro BA</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -8462,17 +8462,17 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>866732956777533</t>
+          <t>565314496863790</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/866732956777533</t>
+          <t>https://www.facebook.com/groups/565314496863790</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>Mercadão Imobiliário Bauru</t>
+          <t>Porto Seguro Negócios</t>
         </is>
       </c>
       <c r="G229" s="4" t="n">
@@ -8482,12 +8482,12 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Seguro BA</t>
+          <t>Porto Seguro BA</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -8497,17 +8497,17 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>2421592694770375</t>
+          <t>907329209279184</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2421592694770375</t>
+          <t>https://www.facebook.com/groups/907329209279184</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>SÓ IMÓVEIS</t>
+          <t>PORTO SEGURO-BA (ALUGUEL)</t>
         </is>
       </c>
       <c r="G230" s="4" t="n">
@@ -8517,12 +8517,12 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Seguro BA</t>
+          <t>Porto Seguro BA</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -8532,17 +8532,17 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>829211013821707</t>
+          <t>906806002720893</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/829211013821707</t>
+          <t>https://www.facebook.com/groups/906806002720893</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>IMÓVEIS SOMENTE IMÓVEIS</t>
+          <t>CLASSIFICADOS DE IMÓVEIS PORTO SEGURO</t>
         </is>
       </c>
       <c r="G231" s="4" t="n">
@@ -8672,17 +8672,17 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>171860803214204</t>
+          <t>2907144759568721</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/171860803214204</t>
+          <t>https://www.facebook.com/groups/2907144759568721</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>Bazar de Nilópolis e RJ desapego, vendas e trocas!!!</t>
+          <t>Joga pra Rolo Olinda - Nilópolis</t>
         </is>
       </c>
       <c r="G235" s="4" t="n">
@@ -8707,17 +8707,17 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>2907144759568721</t>
+          <t>171860803214204</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2907144759568721</t>
+          <t>https://www.facebook.com/groups/171860803214204</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>Joga pra Rolo Olinda - Nilópolis</t>
+          <t>Bazar de Nilópolis e RJ desapego, vendas e trocas!!!</t>
         </is>
       </c>
       <c r="G236" s="4" t="n">
@@ -8812,17 +8812,17 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>2744592102528573</t>
+          <t>1805329766173428</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2744592102528573</t>
+          <t>https://www.facebook.com/groups/1805329766173428</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>TUDO DE BOM EM NILÓPOLIS - RJ</t>
+          <t>AIRSOFT BRASIL [NILOPOLIS] RJ</t>
         </is>
       </c>
       <c r="G239" s="4" t="n">
@@ -8847,17 +8847,17 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>1805329766173428</t>
+          <t>2744592102528573</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1805329766173428</t>
+          <t>https://www.facebook.com/groups/2744592102528573</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>AIRSOFT BRASIL [NILOPOLIS] RJ</t>
+          <t>TUDO DE BOM EM NILÓPOLIS - RJ</t>
         </is>
       </c>
       <c r="G240" s="4" t="n">
@@ -8987,17 +8987,17 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>2139617352915385</t>
+          <t>2836528416483830</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2139617352915385</t>
+          <t>https://www.facebook.com/groups/2836528416483830</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>SÓ ÁGIO CASAS E APARTAMENTOS ENTORNO GOIAS</t>
+          <t>agios de imóveis Goiânia</t>
         </is>
       </c>
       <c r="G244" s="4" t="n">
@@ -9022,17 +9022,17 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>2836528416483830</t>
+          <t>877243212316100</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2836528416483830</t>
+          <t>https://www.facebook.com/groups/877243212316100</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>agios de imóveis Goiânia</t>
+          <t>ALUGUEL / VENDA DE IMÓVEIS CASAS APARTAMENTOS GO GOIÁS GOIÂNIA</t>
         </is>
       </c>
       <c r="G245" s="4" t="n">
@@ -9057,17 +9057,17 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>877243212316100</t>
+          <t>265575897677526</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/877243212316100</t>
+          <t>https://www.facebook.com/groups/265575897677526</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>ALUGUEL / VENDA DE IMÓVEIS CASAS APARTAMENTOS GO GOIÁS GOIÂNIA</t>
+          <t>OLX 24h Valparaíso de Goiás e Regiao - GO ⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="G246" s="4" t="n">
@@ -9127,17 +9127,17 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>265575897677526</t>
+          <t>690510981006466</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/265575897677526</t>
+          <t>https://www.facebook.com/groups/690510981006466</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>OLX 24h Valparaíso de Goiás e Regiao - GO ⭐⭐⭐⭐⭐</t>
+          <t>Comprar e vender imóveis Goianira e região</t>
         </is>
       </c>
       <c r="G248" s="4" t="n">
@@ -9162,17 +9162,17 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>690510981006466</t>
+          <t>512217458978057</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/690510981006466</t>
+          <t>https://www.facebook.com/groups/512217458978057</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>Comprar e vender imóveis Goianira e região</t>
+          <t>Compra e venda de imóveis em Goiânia</t>
         </is>
       </c>
       <c r="G249" s="4" t="n">
@@ -9197,17 +9197,17 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>512217458978057</t>
+          <t>1034061346680705</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/512217458978057</t>
+          <t>https://www.facebook.com/groups/1034061346680705</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>Compra e venda de imóveis em Goiânia</t>
+          <t>Venda de imóveis em Goiânia e Aparecida</t>
         </is>
       </c>
       <c r="G250" s="4" t="n">
@@ -9232,17 +9232,17 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>1034061346680705</t>
+          <t>1827281121503216</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1034061346680705</t>
+          <t>https://www.facebook.com/groups/1827281121503216</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>Venda de imóveis em Goiânia e Aparecida</t>
+          <t>Compra e venda de imovéis GOIÁS.</t>
         </is>
       </c>
       <c r="G251" s="4" t="n">
@@ -9267,17 +9267,17 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>1487263221552784</t>
+          <t>1513714875897184</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1487263221552784</t>
+          <t>https://www.facebook.com/groups/1513714875897184</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>Imóveis para Venda e Aluguel em Bauru</t>
+          <t>Compras e Vendas em Bauru-SP e Região</t>
         </is>
       </c>
       <c r="G252" s="4" t="n">
@@ -9302,17 +9302,17 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>803279393384383</t>
+          <t>1487263221552784</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/803279393384383</t>
+          <t>https://www.facebook.com/groups/1487263221552784</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>OLX BAURU</t>
+          <t>Imóveis para Venda e Aluguel em Bauru</t>
         </is>
       </c>
       <c r="G253" s="4" t="n">
@@ -9337,17 +9337,17 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>130470603825550</t>
+          <t>803279393384383</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/130470603825550</t>
+          <t>https://www.facebook.com/groups/803279393384383</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>IMÓVEL EM BAURU</t>
+          <t>OLX BAURU</t>
         </is>
       </c>
       <c r="G254" s="4" t="n">
@@ -9372,17 +9372,17 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>305099104041858</t>
+          <t>130470603825550</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/305099104041858</t>
+          <t>https://www.facebook.com/groups/130470603825550</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>casa para alugar direto com o proprietário bauru</t>
+          <t>IMÓVEL EM BAURU</t>
         </is>
       </c>
       <c r="G255" s="4" t="n">
@@ -9407,17 +9407,17 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>399629210138656</t>
+          <t>305099104041858</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/399629210138656</t>
+          <t>https://www.facebook.com/groups/305099104041858</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>ALUGUEL E VENDA DE IMOVEIS DA REGIÃO DE BAURU SP</t>
+          <t>casa para alugar direto com o proprietário bauru</t>
         </is>
       </c>
       <c r="G256" s="4" t="n">
@@ -9442,17 +9442,17 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>515680167820540</t>
+          <t>399629210138656</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/515680167820540</t>
+          <t>https://www.facebook.com/groups/399629210138656</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>casa para alugar em Bauru/SP</t>
+          <t>ALUGUEL E VENDA DE IMOVEIS DA REGIÃO DE BAURU SP</t>
         </is>
       </c>
       <c r="G257" s="4" t="n">
@@ -9477,17 +9477,17 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>384755157164407</t>
+          <t>515680167820540</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/384755157164407</t>
+          <t>https://www.facebook.com/groups/515680167820540</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>ALUGA em Bauru e Divulgue seu negocio</t>
+          <t>casa para alugar em Bauru/SP</t>
         </is>
       </c>
       <c r="G258" s="4" t="n">
@@ -9512,17 +9512,17 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>572847752900820</t>
+          <t>773161699403310</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/572847752900820</t>
+          <t>https://www.facebook.com/groups/773161699403310</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>Apartamentos, Casas e Terrenos em Bauru</t>
+          <t>Casas Bauru e região, venda e aluga</t>
         </is>
       </c>
       <c r="G259" s="4" t="n">
@@ -9547,17 +9547,17 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>773161699403310</t>
+          <t>384755157164407</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/773161699403310</t>
+          <t>https://www.facebook.com/groups/384755157164407</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>Casas Bauru e região, venda e aluga</t>
+          <t>ALUGA em Bauru e Divulgue seu negocio</t>
         </is>
       </c>
       <c r="G260" s="4" t="n">
@@ -9582,17 +9582,17 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>1309994755699231</t>
+          <t>460142850754267</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1309994755699231</t>
+          <t>https://www.facebook.com/groups/460142850754267</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>Aluguel de Casas e Aptos Bauru/SP</t>
+          <t>Venda e Aluguel de Imoveis Bauru e Região</t>
         </is>
       </c>
       <c r="G261" s="4" t="n">
@@ -9652,17 +9652,17 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>1668623793197329</t>
+          <t>563231668258995</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1668623793197329</t>
+          <t>https://www.facebook.com/groups/563231668258995</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>Imóveis a venda Cachoeira do Sul</t>
+          <t>Residencial Campo Belo | Cachoeirinha/ RS</t>
         </is>
       </c>
       <c r="G263" s="4" t="n">
@@ -9687,17 +9687,17 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>563231668258995</t>
+          <t>1411875775703109</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/563231668258995</t>
+          <t>https://www.facebook.com/groups/1411875775703109</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>Residencial Campo Belo | Cachoeirinha/ RS</t>
+          <t>Bairro Betania Cachoeirinha Rs</t>
         </is>
       </c>
       <c r="G264" s="4" t="n">
@@ -9722,17 +9722,17 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>1411875775703109</t>
+          <t>1668623793197329</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1411875775703109</t>
+          <t>https://www.facebook.com/groups/1668623793197329</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>Bairro Betania Cachoeirinha Rs</t>
+          <t>Imóveis a venda Cachoeira do Sul</t>
         </is>
       </c>
       <c r="G265" s="4" t="n">
@@ -9757,17 +9757,17 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>614390027748628</t>
+          <t>1068182369953102</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/614390027748628</t>
+          <t>https://www.facebook.com/groups/1068182369953102</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>brick de casas/venda da chave/🔑🏠Cachoeirinha e região metropolitana</t>
+          <t>Aluguel e Venda de Imóveis ( Cachoeira do Sul - RS )</t>
         </is>
       </c>
       <c r="G266" s="4" t="n">
@@ -9792,17 +9792,17 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>1068182369953102</t>
+          <t>614390027748628</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1068182369953102</t>
+          <t>https://www.facebook.com/groups/614390027748628</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>Aluguel e Venda de Imóveis ( Cachoeira do Sul - RS )</t>
+          <t>brick de casas/venda da chave/🔑🏠Cachoeirinha e região metropolitana</t>
         </is>
       </c>
       <c r="G267" s="4" t="n">
@@ -9827,17 +9827,17 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>665256060169807</t>
+          <t>695201357272224</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/665256060169807</t>
+          <t>https://www.facebook.com/groups/695201357272224</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>Classificados Imóveis Cachoeira Do Sul</t>
+          <t>Brick De Motos Cachoeirinha &amp; Gravatai RS</t>
         </is>
       </c>
       <c r="G268" s="4" t="n">
@@ -9862,17 +9862,17 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>695201357272224</t>
+          <t>665256060169807</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/695201357272224</t>
+          <t>https://www.facebook.com/groups/665256060169807</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>Brick De Motos Cachoeirinha &amp; Gravatai RS</t>
+          <t>Classificados Imóveis Cachoeira Do Sul</t>
         </is>
       </c>
       <c r="G269" s="4" t="n">
@@ -10002,17 +10002,17 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>723710771051029</t>
+          <t>2836528416483830</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/723710771051029</t>
+          <t>https://www.facebook.com/groups/2836528416483830</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>Alugueis e vendas de imóveis- Goiânia e região</t>
+          <t>agios de imóveis Goiânia</t>
         </is>
       </c>
       <c r="G273" s="4" t="n">
@@ -10037,17 +10037,17 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>2836528416483830</t>
+          <t>723710771051029</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2836528416483830</t>
+          <t>https://www.facebook.com/groups/723710771051029</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>agios de imóveis Goiânia</t>
+          <t>Alugueis e vendas de imóveis- Goiânia e região</t>
         </is>
       </c>
       <c r="G274" s="4" t="n">
@@ -10177,17 +10177,17 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>1439718522985464</t>
+          <t>806832416413410</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1439718522985464</t>
+          <t>https://www.facebook.com/groups/806832416413410</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>SOMENTE ALUGUÉIS DE IMÓVEIS_GOIÂNIA</t>
+          <t>Negócios Imobiliários</t>
         </is>
       </c>
       <c r="G278" s="4" t="n">
@@ -10212,17 +10212,17 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>806832416413410</t>
+          <t>399056583556695</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/806832416413410</t>
+          <t>https://www.facebook.com/groups/399056583556695</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>Negócios Imobiliários</t>
+          <t>Venda de Imóveis Goiânia</t>
         </is>
       </c>
       <c r="G279" s="4" t="n">
@@ -10247,17 +10247,17 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>779625258754835</t>
+          <t>1439718522985464</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/779625258754835</t>
+          <t>https://www.facebook.com/groups/1439718522985464</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>Compra e Venda de Imoveis Goiânia e Aparecida</t>
+          <t>SOMENTE ALUGUÉIS DE IMÓVEIS_GOIÂNIA</t>
         </is>
       </c>
       <c r="G280" s="4" t="n">
@@ -10282,17 +10282,17 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>399056583556695</t>
+          <t>779625258754835</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/399056583556695</t>
+          <t>https://www.facebook.com/groups/779625258754835</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>Venda de Imóveis Goiânia</t>
+          <t>Compra e Venda de Imoveis Goiânia e Aparecida</t>
         </is>
       </c>
       <c r="G281" s="4" t="n">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Minas</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -10317,17 +10317,17 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>359524615347398</t>
+          <t>398532924181631</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/359524615347398</t>
+          <t>https://www.facebook.com/groups/398532924181631</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>Venda e aluguel de imóveis - Brasilia de Minas</t>
+          <t>Aluga casa é barracão em Para de Minas mg</t>
         </is>
       </c>
       <c r="G282" s="4" t="n">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Minas</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -10352,17 +10352,17 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>398532924181631</t>
+          <t>359524615347398</t>
         </is>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/398532924181631</t>
+          <t>https://www.facebook.com/groups/359524615347398</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>Aluga casa é barracão em Para de Minas mg</t>
+          <t>Venda e aluguel de imóveis - Brasilia de Minas</t>
         </is>
       </c>
       <c r="G283" s="4" t="n">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Minas</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Minas</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -10422,17 +10422,17 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>206552726959115</t>
+          <t>1757058971308798</t>
         </is>
       </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/206552726959115</t>
+          <t>https://www.facebook.com/groups/1757058971308798</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>MARIA DA FÉ-MG! COMPRA, VENDE E ALUGA! MELHORES NEGÓCIOS IMOBILIÁRIOS!</t>
+          <t>aluguel de imóveis Leopoldina Minas Gerais</t>
         </is>
       </c>
       <c r="G285" s="4" t="n">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Minas</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Minas</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -10492,17 +10492,17 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>209340959190268</t>
+          <t>834497886662995</t>
         </is>
       </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/209340959190268</t>
+          <t>https://www.facebook.com/groups/834497886662995</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>COMPRA/VENDA/ALUGUEL DE IMÓVEIS PARÁ DE MINAS E REGIÃO</t>
+          <t>aluga_ se traca e vende. (Para de Minas mg)</t>
         </is>
       </c>
       <c r="G287" s="4" t="n">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Minas</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Minas</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -10562,17 +10562,17 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>2760350354248237</t>
+          <t>209340959190268</t>
         </is>
       </c>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2760350354248237</t>
+          <t>https://www.facebook.com/groups/209340959190268</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>Aluguel Com Preço Justo Minas Gerais - MG32</t>
+          <t>COMPRA/VENDA/ALUGUEL DE IMÓVEIS PARÁ DE MINAS E REGIÃO</t>
         </is>
       </c>
       <c r="G289" s="4" t="n">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Minas</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -10597,17 +10597,17 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>834497886662995</t>
+          <t>2760350354248237</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/834497886662995</t>
+          <t>https://www.facebook.com/groups/2760350354248237</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>aluga_ se traca e vende. (Para de Minas mg)</t>
+          <t>Aluguel Com Preço Justo Minas Gerais - MG32</t>
         </is>
       </c>
       <c r="G290" s="4" t="n">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Minas</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -10632,17 +10632,17 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>259037250898211</t>
+          <t>323362524477201</t>
         </is>
       </c>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/259037250898211</t>
+          <t>https://www.facebook.com/groups/323362524477201</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>Rio Pardo de Minas, MG - Oportunidades de negócios (compra, venda, troca)</t>
+          <t>Betim Imóveis</t>
         </is>
       </c>
       <c r="G291" s="4" t="n">
@@ -10842,17 +10842,17 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>1596096200706854</t>
+          <t>1226537672108843</t>
         </is>
       </c>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1596096200706854</t>
+          <t>https://www.facebook.com/groups/1226537672108843</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>ALUGA E VENDAS DE IMÓVEIS</t>
+          <t>IMÓVEIS DIRETO COM PROPRIETÁRIO RC</t>
         </is>
       </c>
       <c r="G297" s="4" t="n">
@@ -10877,17 +10877,17 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>1226537672108843</t>
+          <t>1628879560986072</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1226537672108843</t>
+          <t>https://www.facebook.com/groups/1628879560986072</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>IMÓVEIS DIRETO COM PROPRIETÁRIO RC</t>
+          <t>Locação e venda de imóveis</t>
         </is>
       </c>
       <c r="G298" s="4" t="n">
@@ -10912,17 +10912,17 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>1628879560986072</t>
+          <t>1762522773789566</t>
         </is>
       </c>
       <c r="E299" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1628879560986072</t>
+          <t>https://www.facebook.com/groups/1762522773789566</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>Locação e venda de imóveis</t>
+          <t>Classificados Imobiliários</t>
         </is>
       </c>
       <c r="G299" s="4" t="n">
@@ -10947,17 +10947,17 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>1762522773789566</t>
+          <t>1596096200706854</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1762522773789566</t>
+          <t>https://www.facebook.com/groups/1596096200706854</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
         <is>
-          <t>Classificados Imobiliários</t>
+          <t>ALUGA E VENDAS DE IMÓVEIS</t>
         </is>
       </c>
       <c r="G300" s="4" t="n">
@@ -10982,17 +10982,17 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>1465099043803433</t>
+          <t>1901615006579509</t>
         </is>
       </c>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1465099043803433</t>
+          <t>https://www.facebook.com/groups/1901615006579509</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>Casas a venda direto com o propietario</t>
+          <t>Imóveis a venda!🚀</t>
         </is>
       </c>
       <c r="G301" s="4" t="n">
@@ -11087,17 +11087,17 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>1229094698228730</t>
+          <t>647314668650553</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1229094698228730</t>
+          <t>https://www.facebook.com/groups/647314668650553</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>OLX FLORIANÓPOLIS-SC</t>
+          <t>SÓ IMOVEIS PALHOÇA</t>
         </is>
       </c>
       <c r="G304" s="4" t="n">
@@ -11122,17 +11122,17 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>647314668650553</t>
+          <t>1229094698228730</t>
         </is>
       </c>
       <c r="E305" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/647314668650553</t>
+          <t>https://www.facebook.com/groups/1229094698228730</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>SÓ IMOVEIS PALHOÇA</t>
+          <t>OLX FLORIANÓPOLIS-SC</t>
         </is>
       </c>
       <c r="G305" s="4" t="n">
@@ -11157,17 +11157,17 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>245985826631088</t>
+          <t>1241533163624160</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/245985826631088</t>
+          <t>https://www.facebook.com/groups/1241533163624160</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>INGLESES ,FLORIANOPOLIS SC. COMPRAR, VENDER E ALUGAR IMÓVEIS!</t>
+          <t>ALUGUEL DE KITNET NA PALHOÇA G. FLORIANÓPOLIS</t>
         </is>
       </c>
       <c r="G306" s="4" t="n">
@@ -11192,17 +11192,17 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>396016307182969</t>
+          <t>245985826631088</t>
         </is>
       </c>
       <c r="E307" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/396016307182969</t>
+          <t>https://www.facebook.com/groups/245985826631088</t>
         </is>
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>Negócios Já - Grande Florianópolis / SC</t>
+          <t>INGLESES ,FLORIANOPOLIS SC. COMPRAR, VENDER E ALUGAR IMÓVEIS!</t>
         </is>
       </c>
       <c r="G307" s="4" t="n">
@@ -11262,17 +11262,17 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>1241533163624160</t>
+          <t>495212733952543</t>
         </is>
       </c>
       <c r="E309" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1241533163624160</t>
+          <t>https://www.facebook.com/groups/495212733952543</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>ALUGUEL DE KITNET NA PALHOÇA G. FLORIANÓPOLIS</t>
+          <t>Imóveis Florianópolis - SC</t>
         </is>
       </c>
       <c r="G309" s="4" t="n">
@@ -11297,17 +11297,17 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>495212733952543</t>
+          <t>361173880687459</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/495212733952543</t>
+          <t>https://www.facebook.com/groups/361173880687459</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>Imóveis Florianópolis - SC</t>
+          <t>Classificados Florianópolis SC - Vendas e Trocas</t>
         </is>
       </c>
       <c r="G310" s="4" t="n">
@@ -11332,17 +11332,17 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>361173880687459</t>
+          <t>396016307182969</t>
         </is>
       </c>
       <c r="E311" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/361173880687459</t>
+          <t>https://www.facebook.com/groups/396016307182969</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>Classificados Florianópolis SC - Vendas e Trocas</t>
+          <t>Negócios Já - Grande Florianópolis / SC</t>
         </is>
       </c>
       <c r="G311" s="4" t="n">
@@ -11577,17 +11577,17 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>806832416413410</t>
+          <t>1637085013193013</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/806832416413410</t>
+          <t>https://www.facebook.com/groups/1637085013193013</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>Negócios Imobiliários</t>
+          <t>MERCADO IMOBILIÁRIO DE SALTO E REGIÃO</t>
         </is>
       </c>
       <c r="G318" s="4" t="n">
@@ -11612,17 +11612,17 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>2421592694770375</t>
+          <t>806832416413410</t>
         </is>
       </c>
       <c r="E319" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2421592694770375</t>
+          <t>https://www.facebook.com/groups/806832416413410</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
-          <t>SÓ IMÓVEIS</t>
+          <t>Negócios Imobiliários</t>
         </is>
       </c>
       <c r="G319" s="4" t="n">
@@ -11647,17 +11647,17 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>1390556161163555</t>
+          <t>2421592694770375</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1390556161163555</t>
+          <t>https://www.facebook.com/groups/2421592694770375</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>Negócios Imobiliários</t>
+          <t>SÓ IMÓVEIS</t>
         </is>
       </c>
       <c r="G320" s="4" t="n">
@@ -11682,17 +11682,17 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>2202481403313873</t>
+          <t>1390556161163555</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2202481403313873</t>
+          <t>https://www.facebook.com/groups/1390556161163555</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
-          <t>Classificados Compra, Venda e Locação de Imóveis em Promissão - SP</t>
+          <t>Negócios Imobiliários</t>
         </is>
       </c>
       <c r="G321" s="4" t="n">
@@ -11822,17 +11822,17 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>2282725061816147</t>
+          <t>1339066136210416</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2282725061816147</t>
+          <t>https://www.facebook.com/groups/1339066136210416</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>Vende fácil bairro Matão e região</t>
+          <t>MATÃO &amp; REGIAO - Classificados.</t>
         </is>
       </c>
       <c r="G325" s="4" t="n">
@@ -11857,17 +11857,17 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>352107458185591</t>
+          <t>2282725061816147</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/352107458185591</t>
+          <t>https://www.facebook.com/groups/2282725061816147</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>TROCA E VENDA MATÃO</t>
+          <t>Vende fácil bairro Matão e região</t>
         </is>
       </c>
       <c r="G326" s="4" t="n">
@@ -11892,17 +11892,17 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>1851224705733412</t>
+          <t>352107458185591</t>
         </is>
       </c>
       <c r="E327" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1851224705733412</t>
+          <t>https://www.facebook.com/groups/352107458185591</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
-          <t>venda de casas Matão</t>
+          <t>TROCA E VENDA MATÃO</t>
         </is>
       </c>
       <c r="G327" s="4" t="n">
@@ -11962,17 +11962,17 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>763542513799697</t>
+          <t>1851224705733412</t>
         </is>
       </c>
       <c r="E329" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/763542513799697</t>
+          <t>https://www.facebook.com/groups/1851224705733412</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>classificados, troca, compras e vendas de matão</t>
+          <t>venda de casas Matão</t>
         </is>
       </c>
       <c r="G329" s="4" t="n">
@@ -11997,17 +11997,17 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>487908569130543</t>
+          <t>790453447697198</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/487908569130543</t>
+          <t>https://www.facebook.com/groups/790453447697198</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>OLX Classificados Matão-sp Região</t>
+          <t>Vendas Matão</t>
         </is>
       </c>
       <c r="G330" s="4" t="n">
@@ -12032,17 +12032,17 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>602794168361227</t>
+          <t>472559136105198</t>
         </is>
       </c>
       <c r="E331" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/602794168361227</t>
+          <t>https://www.facebook.com/groups/472559136105198</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>Classificados com preço Matão</t>
+          <t>CLASSIFICADOS MATÃO E REGIÃO</t>
         </is>
       </c>
       <c r="G331" s="4" t="n">
@@ -12572,24 +12572,24 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Caonze Rio de Janeiro</t>
+          <t>Rio de Janeiro RJ</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Janeiro</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>bairro</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
         <v>10</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>60000</v>
+        <v>6748000</v>
       </c>
     </row>
     <row r="9">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Pessoa</t>
+          <t>João Pessoa</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -12842,7 +12842,7 @@
         <v>10</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>364254</v>
+        <v>11451245</v>
       </c>
     </row>
     <row r="20">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Leopoldo</t>
+          <t>São Leopoldo</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -12940,12 +12940,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Seguro BA</t>
+          <t>Porto Seguro BA</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Minas</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
